--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/设备信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/设备信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,14 +519,8 @@
           <t>OFFE00086780</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>64</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CloudEngine 16800 V200R019C10SPC800</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>GA</t>
@@ -555,11 +549,7 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -597,14 +587,8 @@
           <t>OFFE00082295</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>76</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CloudEngine 9800 V300R023C11</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>GA</t>
@@ -633,11 +617,7 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -675,9 +655,7 @@
           <t>02356FQH</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>64</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -687,11 +665,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -729,9 +703,7 @@
           <t>02356TXY</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>76</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -741,11 +713,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -783,14 +751,8 @@
           <t>OFFE01128327</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>585</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Atlas 900 A3 SuperPoD 1.0.T33</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>GA</t>
@@ -819,11 +781,7 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -2050,6 +2008,348 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CloudEngine 16800</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>OFFE00086780</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>64</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CloudEngine 16800 V200R020C10SPC800</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2019-09-30</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2019-09-30</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2035-12-31</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2045-12-31</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>02356FQH</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>交换机</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CloudEngine 9800</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>OFFE00082295</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>76</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CloudEngine 9800 V200R025C00</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2019-07-30</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2019-07-30</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2035-12-31</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2045-12-31</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>02356TXY</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>交换机</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CloudEngine XH16800</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>02356FQH</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>64</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>02356FQH</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>交换机</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CloudEngine XH9000</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>02356TXY</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>76</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>02356TXY</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>交换机</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Atlas 900 A3 SuperPoD</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>OFFE01128327</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>585</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Atlas 900 A3 SuperPoD 1.0.T23</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2028-06-30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2033-06-30</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>02315KEE</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>智算服务器</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/设备信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/设备信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2019,14 +2019,8 @@
           <t>OFFE00086780</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>64</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>CloudEngine 16800 V200R020C10SPC800</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>GA</t>
@@ -2055,11 +2049,7 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -2097,14 +2087,8 @@
           <t>OFFE00082295</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>76</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>CloudEngine 9800 V200R025C00</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>GA</t>
@@ -2133,11 +2117,7 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -2175,9 +2155,7 @@
           <t>02356FQH</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>64</v>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
@@ -2187,11 +2165,7 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -2229,9 +2203,7 @@
           <t>02356TXY</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>76</v>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
@@ -2241,11 +2213,7 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -2283,14 +2251,8 @@
           <t>OFFE01128327</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>585</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Atlas 900 A3 SuperPoD 1.0.T23</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>GA</t>
@@ -2319,32 +2281,370 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>02315KEE</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>智算服务器</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CloudEngine 16800</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>OFFE00086780</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>64</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CloudEngine 16800 V200R020C10SPC800</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2019-09-30</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2019-09-30</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2035-12-31</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2045-12-31</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
         <is>
           <t>自动解析</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>V2.2_20260614213043_DRB</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>02356FQH</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>交换机</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CloudEngine 9800</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>OFFE00082295</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>76</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CloudEngine 9800 V200R025C00</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2019-07-30</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2019-07-30</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2035-12-31</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2045-12-31</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>02356TXY</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>交换机</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CloudEngine XH16800</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>02356FQH</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>64</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>02356FQH</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>交换机</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CloudEngine XH9000</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>02356TXY</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>76</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>02356TXY</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>交换机</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Atlas 900 A3 SuperPoD</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>OFFE01128327</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>585</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Atlas 900 A3 SuperPoD 1.0.T23</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2028-06-30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2033-06-30</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>02315KEE</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>主设备</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>智算服务器</t>
         </is>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/设备信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/设备信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,8 +519,14 @@
           <t>OFFE00086780</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CloudEngine 16800 V200R020C10SPC800</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>GA</t>
@@ -549,7 +555,11 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -587,8 +597,14 @@
           <t>OFFE00082295</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>76</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CloudEngine 9800 V200R025C00</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>GA</t>
@@ -617,7 +633,11 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -655,7 +675,9 @@
           <t>02356FQH</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>64</v>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -665,7 +687,11 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -703,7 +729,9 @@
           <t>02356TXY</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>76</v>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -713,7 +741,11 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -751,8 +783,14 @@
           <t>OFFE01128327</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>585</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Atlas 900 A3 SuperPoD 1.0.T23</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>GA</t>
@@ -781,7 +819,11 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -2319,14 +2361,8 @@
           <t>OFFE00086780</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>64</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>CloudEngine 16800 V200R020C10SPC800</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>GA</t>
@@ -2355,11 +2391,7 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2397,14 +2429,8 @@
           <t>OFFE00082295</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>76</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>CloudEngine 9800 V200R025C00</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>GA</t>
@@ -2433,11 +2459,7 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2475,9 +2497,7 @@
           <t>02356FQH</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>64</v>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
@@ -2487,11 +2507,7 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2529,9 +2545,7 @@
           <t>02356TXY</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>76</v>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
@@ -2541,11 +2555,7 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2583,14 +2593,8 @@
           <t>OFFE01128327</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>585</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Atlas 900 A3 SuperPoD 1.0.T23</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>GA</t>
@@ -2619,11 +2623,7 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -2645,6 +2645,306 @@
         </is>
       </c>
       <c r="R36" t="inlineStr">
+        <is>
+          <t>智算服务器</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CloudEngine 16800</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>OFFE00086780</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2019-09-30</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2019-09-30</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2035-12-31</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2045-12-31</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>02356FQH</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>交换机</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CloudEngine 9800</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>OFFE00082295</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2019-07-30</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2019-07-30</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2035-12-31</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2045-12-31</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>02356TXY</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>交换机</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CloudEngine XH16800</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>02356FQH</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>02356FQH</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>交换机</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CloudEngine XH9000</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>02356TXY</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>02356TXY</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>交换机</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Atlas 900 A3 SuperPoD</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>OFFE01128327</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2028-06-30</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2033-06-30</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>02315KEE</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>主设备</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>智算服务器</t>
         </is>
